--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -108,10 +108,10 @@
     <t>Win battles a total of 5 or more times</t>
   </si>
   <si>
-    <t>いずれかのキャラLvを4以上にする</t>
-  </si>
-  <si>
-    <t>Increase one character's level to 4 or higher</t>
+    <t>いずれかのキャラLvを3以上にする</t>
+  </si>
+  <si>
+    <t>Increase one character's level to 3 or higher</t>
   </si>
   <si>
     <t>評価値を累計100以上獲得する</t>
@@ -545,10 +545,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -559,47 +559,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -614,6 +596,36 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -622,7 +634,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -636,37 +656,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -680,11 +680,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -697,7 +697,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -712,7 +712,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,175 +892,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -903,24 +903,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -935,30 +917,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -980,11 +938,27 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1003,6 +977,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1011,145 +1011,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1726,7 +1726,7 @@
         <v>1030</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>-1</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -545,10 +545,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -566,6 +566,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -573,8 +613,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -587,24 +628,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -618,63 +644,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -689,7 +675,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -697,7 +690,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -712,139 +712,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,13 +730,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -886,13 +856,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -903,21 +903,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -940,7 +925,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -949,16 +949,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -978,17 +969,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1003,6 +983,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1011,145 +1011,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2284,7 +2284,7 @@
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2491,7 +2491,7 @@
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2606,7 +2606,7 @@
         <v>3</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2721,7 +2721,7 @@
         <v>5</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2790,7 +2790,7 @@
         <v>5</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="182">
   <si>
     <t>Id</t>
   </si>
@@ -210,10 +210,10 @@
     <t>Increase the level of 3 or more characters to 15 or higher</t>
   </si>
   <si>
-    <t>バトルで覚醒スキルを1回以上使用する</t>
-  </si>
-  <si>
-    <t>Use Awakening Skills at least 1 in battle</t>
+    <t>バトルで覚醒スキルを3回以上使用する</t>
+  </si>
+  <si>
+    <t>Use Awakening Skills at least 3 in battle</t>
   </si>
   <si>
     <t>バトルで交代を1回以上使用する</t>
@@ -222,6 +222,18 @@
     <t>Perform a substitution at least 1 in battle</t>
   </si>
   <si>
+    <t>アイテムを使用していずれかのキャラの属性適正値を上げる</t>
+  </si>
+  <si>
+    <t>Attribute up one character by using an item</t>
+  </si>
+  <si>
+    <t>ダンジョン内で呪い状態から回復する</t>
+  </si>
+  <si>
+    <t>Recovery curse in dungeon</t>
+  </si>
+  <si>
     <t>亡国の宮殿跡地のボスを撃破する</t>
   </si>
   <si>
@@ -435,7 +447,13 @@
     <t>TacticsLvupCount</t>
   </si>
   <si>
-    <t>Nu消費レベルアップ回数</t>
+    <t>アイテム消費レベルアップ回数</t>
+  </si>
+  <si>
+    <t>TacticsAttributeupCount</t>
+  </si>
+  <si>
+    <t>アイテム消費属性適正値アップ回数</t>
   </si>
   <si>
     <t>BattleScore</t>
@@ -466,6 +484,12 @@
   </si>
   <si>
     <t>ステージボスを倒している</t>
+  </si>
+  <si>
+    <t>RecoveryCurseCount</t>
+  </si>
+  <si>
+    <t>ダンジョン内で呪いを回復した数</t>
   </si>
   <si>
     <t>UseAwakeSkillCount</t>
@@ -546,8 +570,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -560,6 +584,57 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -568,6 +643,61 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -590,112 +720,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -712,13 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,103 +748,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,13 +772,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +868,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,19 +880,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -903,6 +927,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -924,47 +978,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -986,15 +1001,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1003,6 +1009,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1011,145 +1035,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1476,7 +1500,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9.54545454545454"/>
@@ -2100,7 +2124,7 @@
         <v>3</v>
       </c>
       <c r="G27">
-        <v>15060</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2117,13 +2141,13 @@
         <v>3010</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>14020</v>
+        <v>11020</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2146,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>14020</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2160,16 +2184,16 @@
         <v>5</v>
       </c>
       <c r="D30">
-        <v>2010</v>
+        <v>1041</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>20</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2183,16 +2207,16 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>1080</v>
+        <v>2020</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1100</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2206,67 +2230,67 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>20010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>5110</v>
+        <v>5070</v>
       </c>
       <c r="B33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>5</v>
       </c>
       <c r="D33">
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>5120</v>
+        <v>5080</v>
       </c>
       <c r="B34">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>1020</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>5130</v>
+        <v>5110</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -2275,13 +2299,13 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>10</v>
@@ -2289,7 +2313,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>5140</v>
+        <v>5120</v>
       </c>
       <c r="B36">
         <v>20</v>
@@ -2298,10 +2322,10 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E36">
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2312,7 +2336,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>5150</v>
+        <v>5130</v>
       </c>
       <c r="B37">
         <v>20</v>
@@ -2321,13 +2345,13 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>1060</v>
+        <v>1030</v>
       </c>
       <c r="E37">
-        <v>5000</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G37">
         <v>10</v>
@@ -2335,145 +2359,145 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>6010</v>
+        <v>5140</v>
       </c>
       <c r="B38">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>14310</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>6020</v>
+        <v>5150</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>2010</v>
+        <v>1060</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="B40">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>1100</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>6040</v>
+        <v>6020</v>
       </c>
       <c r="B41">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>20010</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>6110</v>
+        <v>6030</v>
       </c>
       <c r="B42">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C42">
         <v>6</v>
       </c>
       <c r="D42">
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>10</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>6120</v>
+        <v>6040</v>
       </c>
       <c r="B43">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43">
-        <v>1020</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>6130</v>
+        <v>6110</v>
       </c>
       <c r="B44">
         <v>20</v>
@@ -2482,13 +2506,13 @@
         <v>6</v>
       </c>
       <c r="D44">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -2496,7 +2520,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>6140</v>
+        <v>6120</v>
       </c>
       <c r="B45">
         <v>20</v>
@@ -2505,10 +2529,10 @@
         <v>6</v>
       </c>
       <c r="D45">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E45">
-        <v>3000</v>
+        <v>75</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2519,7 +2543,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>6150</v>
+        <v>6130</v>
       </c>
       <c r="B46">
         <v>20</v>
@@ -2528,13 +2552,13 @@
         <v>6</v>
       </c>
       <c r="D46">
-        <v>1060</v>
+        <v>1030</v>
       </c>
       <c r="E46">
-        <v>7500</v>
+        <v>20</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G46">
         <v>10</v>
@@ -2542,99 +2566,99 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>7010</v>
+        <v>6140</v>
       </c>
       <c r="B47">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>3000</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>7020</v>
+        <v>6150</v>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>1060</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>7500</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>20010</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>7110</v>
+        <v>7010</v>
       </c>
       <c r="B49">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49">
-        <v>1031</v>
+        <v>2010</v>
       </c>
       <c r="E49">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>7120</v>
+        <v>7020</v>
       </c>
       <c r="B50">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C50">
         <v>7</v>
       </c>
       <c r="D50">
-        <v>3010</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>7130</v>
+        <v>7110</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -2643,13 +2667,13 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>3020</v>
+        <v>1031</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51">
         <v>10</v>
@@ -2657,85 +2681,85 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>8010</v>
+        <v>7120</v>
       </c>
       <c r="B52">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>1012</v>
+        <v>3010</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52">
-        <v>15050</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>8020</v>
+        <v>7130</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>3020</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53">
-        <v>20010</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>8110</v>
+        <v>8010</v>
       </c>
       <c r="B54">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C54">
         <v>8</v>
       </c>
       <c r="D54">
-        <v>1031</v>
+        <v>1012</v>
       </c>
       <c r="E54">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>8120</v>
+        <v>8020</v>
       </c>
       <c r="B55">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55">
-        <v>7060</v>
+        <v>10</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -2744,12 +2768,12 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>8130</v>
+        <v>8110</v>
       </c>
       <c r="B56">
         <v>20</v>
@@ -2758,13 +2782,13 @@
         <v>8</v>
       </c>
       <c r="D56">
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G56">
         <v>10</v>
@@ -2772,22 +2796,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>9110</v>
+        <v>8120</v>
       </c>
       <c r="B57">
         <v>20</v>
       </c>
       <c r="C57">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57">
-        <v>1031</v>
+        <v>7060</v>
       </c>
       <c r="E57">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G57">
         <v>10</v>
@@ -2795,16 +2819,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>9120</v>
+        <v>8130</v>
       </c>
       <c r="B58">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58">
-        <v>7060</v>
+        <v>1070</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -2818,7 +2842,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>9130</v>
+        <v>9110</v>
       </c>
       <c r="B59">
         <v>20</v>
@@ -2827,15 +2851,61 @@
         <v>9</v>
       </c>
       <c r="D59">
+        <v>1031</v>
+      </c>
+      <c r="E59">
+        <v>30</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>9120</v>
+      </c>
+      <c r="B60">
+        <v>20</v>
+      </c>
+      <c r="C60">
+        <v>9</v>
+      </c>
+      <c r="D60">
+        <v>7060</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>9130</v>
+      </c>
+      <c r="B61">
+        <v>20</v>
+      </c>
+      <c r="C61">
+        <v>9</v>
+      </c>
+      <c r="D61">
         <v>1070</v>
       </c>
-      <c r="E59">
+      <c r="E61">
         <v>5</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>10</v>
       </c>
     </row>
@@ -2848,7 +2918,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="5.54545454545455" customWidth="1"/>
@@ -3403,7 +3473,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>5110</v>
+        <v>5070</v>
       </c>
       <c r="B33" t="s">
         <v>74</v>
@@ -3420,7 +3490,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>5120</v>
+        <v>5080</v>
       </c>
       <c r="B34" t="s">
         <v>76</v>
@@ -3437,7 +3507,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>5130</v>
+        <v>5110</v>
       </c>
       <c r="B35" t="s">
         <v>78</v>
@@ -3454,7 +3524,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>5140</v>
+        <v>5120</v>
       </c>
       <c r="B36" t="s">
         <v>80</v>
@@ -3471,7 +3541,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>5150</v>
+        <v>5130</v>
       </c>
       <c r="B37" t="s">
         <v>82</v>
@@ -3488,7 +3558,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>6010</v>
+        <v>5140</v>
       </c>
       <c r="B38" t="s">
         <v>84</v>
@@ -3505,7 +3575,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>6020</v>
+        <v>5150</v>
       </c>
       <c r="B39" t="s">
         <v>86</v>
@@ -3522,7 +3592,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -3539,7 +3609,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>6040</v>
+        <v>6020</v>
       </c>
       <c r="B41" t="s">
         <v>90</v>
@@ -3556,7 +3626,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>6110</v>
+        <v>6030</v>
       </c>
       <c r="B42" t="s">
         <v>92</v>
@@ -3573,7 +3643,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>6120</v>
+        <v>6040</v>
       </c>
       <c r="B43" t="s">
         <v>94</v>
@@ -3590,7 +3660,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>6130</v>
+        <v>6110</v>
       </c>
       <c r="B44" t="s">
         <v>96</v>
@@ -3607,7 +3677,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>6140</v>
+        <v>6120</v>
       </c>
       <c r="B45" t="s">
         <v>98</v>
@@ -3624,7 +3694,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>6150</v>
+        <v>6130</v>
       </c>
       <c r="B46" t="s">
         <v>100</v>
@@ -3641,7 +3711,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>7010</v>
+        <v>6140</v>
       </c>
       <c r="B47" t="s">
         <v>102</v>
@@ -3658,7 +3728,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>7020</v>
+        <v>6150</v>
       </c>
       <c r="B48" t="s">
         <v>104</v>
@@ -3675,7 +3745,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>7110</v>
+        <v>7010</v>
       </c>
       <c r="B49" t="s">
         <v>106</v>
@@ -3692,7 +3762,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>7120</v>
+        <v>7020</v>
       </c>
       <c r="B50" t="s">
         <v>108</v>
@@ -3709,7 +3779,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>7130</v>
+        <v>7110</v>
       </c>
       <c r="B51" t="s">
         <v>110</v>
@@ -3726,16 +3796,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>8010</v>
+        <v>7120</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -3743,16 +3813,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>8020</v>
+        <v>7130</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -3760,16 +3830,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>8110</v>
+        <v>8010</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -3777,7 +3847,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>8120</v>
+        <v>8020</v>
       </c>
       <c r="B55" t="s">
         <v>116</v>
@@ -3794,7 +3864,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>8130</v>
+        <v>8110</v>
       </c>
       <c r="B56" t="s">
         <v>118</v>
@@ -3811,7 +3881,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>9110</v>
+        <v>8120</v>
       </c>
       <c r="B57" t="s">
         <v>120</v>
@@ -3828,7 +3898,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>9120</v>
+        <v>8130</v>
       </c>
       <c r="B58" t="s">
         <v>122</v>
@@ -3845,7 +3915,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>9130</v>
+        <v>9110</v>
       </c>
       <c r="B59" t="s">
         <v>124</v>
@@ -3857,6 +3927,40 @@
         <v>125</v>
       </c>
       <c r="G59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>9120</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>127</v>
+      </c>
+      <c r="G60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>9130</v>
+      </c>
+      <c r="B61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3869,7 +3973,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="15.6363636363636" customWidth="1"/>
@@ -3886,10 +3990,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3897,10 +4001,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3908,10 +4012,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3919,10 +4023,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3930,10 +4034,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3941,10 +4045,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3952,197 +4056,219 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2010</v>
+        <v>1080</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7020</v>
+        <v>3010</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7040</v>
+        <v>3020</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>7050</v>
+        <v>7020</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>7060</v>
+        <v>7040</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>7070</v>
+        <v>7050</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>7080</v>
+        <v>7060</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C21" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>8010</v>
+        <v>7070</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8020</v>
+        <v>7080</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8030</v>
+        <v>8010</v>
       </c>
       <c r="B24" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
+        <v>8020</v>
+      </c>
+      <c r="B25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>8030</v>
+      </c>
+      <c r="B26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>8040</v>
       </c>
-      <c r="B25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" t="s">
-        <v>173</v>
+      <c r="B27" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -569,10 +569,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -583,8 +583,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -598,9 +599,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -613,22 +660,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -641,9 +683,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -659,52 +700,19 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -712,16 +720,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -736,7 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,13 +754,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,13 +790,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,133 +904,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -927,6 +927,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -960,6 +975,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -971,41 +997,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1027,6 +1018,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1035,145 +1035,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2756,7 +2756,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>10</v>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Achievements" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="122">
   <si>
     <t>Id</t>
   </si>
@@ -90,40 +90,40 @@
     <t>Change a comrade's equipment</t>
   </si>
   <si>
-    <t>Rank1の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 1 important tasks</t>
-  </si>
-  <si>
-    <t>累計1回以上出撃する</t>
-  </si>
-  <si>
-    <t>Sortie a total of 1 or more times</t>
-  </si>
-  <si>
-    <t>累計5回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>Win battles a total of 5 or more times</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを3以上にする</t>
-  </si>
-  <si>
-    <t>Increase one character's level to 3 or higher</t>
-  </si>
-  <si>
-    <t>評価値を累計100以上獲得する</t>
-  </si>
-  <si>
-    <t>Accumulate an evaluation value of 100 or more</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が200を超える</t>
-  </si>
-  <si>
-    <t>Total damage dealt exceeds 200</t>
+    <t>Rank{0}の重要課題を全て達成する</t>
+  </si>
+  <si>
+    <t>Complete all Rank {0} important tasks</t>
+  </si>
+  <si>
+    <t>累計{0}回以上出撃する</t>
+  </si>
+  <si>
+    <t>Sortie a total of {0} or more times</t>
+  </si>
+  <si>
+    <t>累計{0}回以上バトルに勝利する</t>
+  </si>
+  <si>
+    <t>Win battles a total of {0} or more times</t>
+  </si>
+  <si>
+    <t>いずれかのキャラLvを{0}以上にする</t>
+  </si>
+  <si>
+    <t>Increase one character's level to {0} or higher</t>
+  </si>
+  <si>
+    <t>評価値を累計{0}以上獲得する</t>
+  </si>
+  <si>
+    <t>Accumulate an evaluation value of {0} or more</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が{0}</t>
+  </si>
+  <si>
+    <t>Total damage dealt exceeds {0}</t>
   </si>
   <si>
     <t>忘れられた山岳遺跡のボスを撃破する</t>
@@ -132,46 +132,13 @@
     <t>Defeat the boss in the Forgotten Mountain Ruins</t>
   </si>
   <si>
-    <t>仲間の封印魔法を2つ以上解放する</t>
-  </si>
-  <si>
-    <t>Unseal 2 or more sealed magic spells on comrades</t>
-  </si>
-  <si>
-    <t>Rank2の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 2 important tasks</t>
-  </si>
-  <si>
-    <t>累計5回以上出撃する</t>
-  </si>
-  <si>
-    <t>Sortie a total of 5 or more times</t>
-  </si>
-  <si>
-    <t>累計20回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>Win battles a total of 20 or more times</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを7以上にする</t>
-  </si>
-  <si>
-    <t>Increase one character's level to 7 or higher</t>
-  </si>
-  <si>
-    <t>評価値を累計500以上獲得する</t>
-  </si>
-  <si>
-    <t>Accumulate an evaluation value of 500 or more</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が1500を超える</t>
-  </si>
-  <si>
-    <t>Total damage dealt exceeds 1500</t>
+    <t>仲間の封印魔法を{0}つ以上解放する</t>
+  </si>
+  <si>
+    <t>Unseal {0} or more sealed magic spells on comrades</t>
+  </si>
+  <si>
+    <t>与ダメージ累計が{0}を超える</t>
   </si>
   <si>
     <t>月影の森のボスを撃破する</t>
@@ -180,46 +147,28 @@
     <t>Defeat the boss in the Moonlit Forest</t>
   </si>
   <si>
-    <t>仲間の封印魔法を4つ以上解放する</t>
-  </si>
-  <si>
-    <t>Unseal 4 or more sealed magic spells on comrades</t>
-  </si>
-  <si>
-    <t>Rank3の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 3 important tasks</t>
-  </si>
-  <si>
     <t>戦争(BattleField)ステージに出撃する</t>
   </si>
   <si>
     <t>Sortie into a Battlefield stage</t>
   </si>
   <si>
-    <t>Rank4の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 4 important tasks</t>
-  </si>
-  <si>
-    <t>3人以上のキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>Increase the level of 3 or more characters to 15 or higher</t>
-  </si>
-  <si>
-    <t>バトルで覚醒スキルを3回以上使用する</t>
-  </si>
-  <si>
-    <t>Use Awakening Skills at least 3 in battle</t>
-  </si>
-  <si>
-    <t>バトルで交代を1回以上使用する</t>
-  </si>
-  <si>
-    <t>Perform a substitution at least 1 in battle</t>
+    <t>3人以上のキャラLvを{0}以上にする</t>
+  </si>
+  <si>
+    <t>Increase the level of {0} or more characters to 3 or higher</t>
+  </si>
+  <si>
+    <t>バトルで覚醒スキルを{0}回以上使用する</t>
+  </si>
+  <si>
+    <t>Use Awakening Skills at least {0} in battle</t>
+  </si>
+  <si>
+    <t>バトルで交代を{0}回以上使用する</t>
+  </si>
+  <si>
+    <t>Perform a substitution at least {0} in battle</t>
   </si>
   <si>
     <t>アイテムを使用していずれかのキャラの属性適正値を上げる</t>
@@ -240,48 +189,6 @@
     <t>Defeat the boss in the Ruins of the Fallen Kingdom</t>
   </si>
   <si>
-    <t>仲間の封印魔法を6つ以上解放する</t>
-  </si>
-  <si>
-    <t>Unseal 6 or more sealed magic spells on comrades</t>
-  </si>
-  <si>
-    <t>Rank5の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 5 important tasks</t>
-  </si>
-  <si>
-    <t>累計10回以上出撃する</t>
-  </si>
-  <si>
-    <t>Sortie a total of 10 or more times</t>
-  </si>
-  <si>
-    <t>累計50回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>Win battles a total of 50 or more times</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを15以上にする</t>
-  </si>
-  <si>
-    <t>Increase one character's level to 15 or higher</t>
-  </si>
-  <si>
-    <t>評価値を累計1500以上獲得する</t>
-  </si>
-  <si>
-    <t>Accumulate an evaluation value of 1500 or more</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が5000を超える</t>
-  </si>
-  <si>
-    <t>Total damage dealt exceeds 5000</t>
-  </si>
-  <si>
     <t>いずれかのキャラをクラスチェンジする</t>
   </si>
   <si>
@@ -294,118 +201,31 @@
     <t>Defeat the boss in the Dark Tower</t>
   </si>
   <si>
-    <t>仲間の封印魔法を8つ以上解放する</t>
-  </si>
-  <si>
-    <t>Unseal 8 or more sealed magic spells on comrades</t>
-  </si>
-  <si>
-    <t>Rank7の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 7 important tasks</t>
-  </si>
-  <si>
-    <t>累計15回以上出撃する</t>
-  </si>
-  <si>
-    <t>Sortie a total of 15 or more times</t>
-  </si>
-  <si>
-    <t>累計75回以上バトルに勝利する</t>
-  </si>
-  <si>
-    <t>Win battles a total of 75 or more times</t>
-  </si>
-  <si>
-    <t>いずれかのキャラLvを20以上にする</t>
-  </si>
-  <si>
-    <t>Increase one character's level to 20 or higher</t>
-  </si>
-  <si>
-    <t>評価値を累計3000以上獲得する</t>
-  </si>
-  <si>
-    <t>Accumulate an evaluation value of 3000 or more</t>
-  </si>
-  <si>
-    <t>与ダメージ累計が7500を超える</t>
-  </si>
-  <si>
-    <t>Total damage dealt exceeds 7500</t>
-  </si>
-  <si>
     <t>天空城のボスを撃破する</t>
   </si>
   <si>
     <t>Defeat the boss in Sky City</t>
   </si>
   <si>
-    <t>Rank8の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 8 important tasks</t>
-  </si>
-  <si>
-    <t>3人以上のキャラLvを25以上にする</t>
-  </si>
-  <si>
-    <t>Increase the level of 3 or more characters to 25 or higher</t>
-  </si>
-  <si>
-    <t>バトルで覚醒スキルを5回以上使用する</t>
-  </si>
-  <si>
-    <t>Use Awakening Skills at least 5 in battle</t>
-  </si>
-  <si>
-    <t>バトルで交代を5回以上使用する</t>
-  </si>
-  <si>
-    <t>Perform a substitution at least 5 in battle</t>
-  </si>
-  <si>
-    <t>Rank9の重要課題を全て達成する</t>
-  </si>
-  <si>
-    <t>Complete all Rank 9 important tasks</t>
-  </si>
-  <si>
-    <t>5人以上のキャラLvを25以上にする</t>
-  </si>
-  <si>
-    <t>Increase the level of 5 or more characters to 25 or higher</t>
-  </si>
-  <si>
-    <t>エインフェリアを2人転送する</t>
-  </si>
-  <si>
-    <t>Transfer 2 Enferia</t>
-  </si>
-  <si>
-    <t>3人以上のキャラをクラスチェンジする</t>
-  </si>
-  <si>
-    <t>Change the class of 3 or more characters</t>
-  </si>
-  <si>
-    <t>5人以上のキャラLvを30以上にする</t>
-  </si>
-  <si>
-    <t>Increase the level of 5 or more characters to 30 or higher</t>
-  </si>
-  <si>
-    <t>エインフェリアを3人転送する</t>
-  </si>
-  <si>
-    <t>Transfer 3 Enferia</t>
-  </si>
-  <si>
-    <t>5人以上のキャラをクラスチェンジする</t>
-  </si>
-  <si>
-    <t>Change the class of 5 or more characters</t>
+    <t>Increase the level of 3 or more characters to {0} or higher</t>
+  </si>
+  <si>
+    <t>5人以上のキャラLvを{0}以上にする</t>
+  </si>
+  <si>
+    <t>Increase the level of 5 or more characters to {0} or higher</t>
+  </si>
+  <si>
+    <t>エインフェリアを{0}人転送する</t>
+  </si>
+  <si>
+    <t>Transfer {0} Enferia</t>
+  </si>
+  <si>
+    <t>{0}人以上のキャラをクラスチェンジする</t>
+  </si>
+  <si>
+    <t>Change the class of {0} or more characters</t>
   </si>
   <si>
     <t>Complete</t>
@@ -570,9 +390,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -583,9 +403,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -599,55 +426,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -660,8 +440,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -677,16 +486,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -698,21 +516,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -720,8 +524,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -736,7 +556,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +568,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,7 +604,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,55 +718,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -832,91 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -927,36 +747,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -975,13 +765,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1004,8 +798,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1021,9 +839,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1035,67 +855,67 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1104,76 +924,76 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3187,13 +3007,13 @@
         <v>2080</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -3204,13 +3024,13 @@
         <v>3010</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -3221,13 +3041,13 @@
         <v>3020</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -3238,13 +3058,13 @@
         <v>3030</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -3255,13 +3075,13 @@
         <v>3040</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -3272,13 +3092,13 @@
         <v>3050</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -3289,13 +3109,13 @@
         <v>3060</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G22" t="s">
         <v>12</v>
@@ -3306,13 +3126,13 @@
         <v>3070</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G23" t="s">
         <v>12</v>
@@ -3323,13 +3143,13 @@
         <v>3080</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -3340,13 +3160,13 @@
         <v>4010</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -3357,13 +3177,13 @@
         <v>4020</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -3374,13 +3194,13 @@
         <v>5010</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
@@ -3391,13 +3211,13 @@
         <v>5020</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -3408,13 +3228,13 @@
         <v>5030</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -3425,13 +3245,13 @@
         <v>5040</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
@@ -3442,13 +3262,13 @@
         <v>5050</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G31" t="s">
         <v>12</v>
@@ -3459,13 +3279,13 @@
         <v>5060</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -3476,13 +3296,13 @@
         <v>5070</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -3493,13 +3313,13 @@
         <v>5080</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
         <v>12</v>
@@ -3510,13 +3330,13 @@
         <v>5110</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
         <v>12</v>
@@ -3527,13 +3347,13 @@
         <v>5120</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -3544,13 +3364,13 @@
         <v>5130</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -3561,13 +3381,13 @@
         <v>5140</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="G38" t="s">
         <v>12</v>
@@ -3578,13 +3398,13 @@
         <v>5150</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -3595,13 +3415,13 @@
         <v>6010</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="G40" t="s">
         <v>12</v>
@@ -3612,13 +3432,13 @@
         <v>6020</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -3629,13 +3449,13 @@
         <v>6030</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -3646,13 +3466,13 @@
         <v>6040</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -3663,13 +3483,13 @@
         <v>6110</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -3680,13 +3500,13 @@
         <v>6120</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
@@ -3697,13 +3517,13 @@
         <v>6130</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -3714,13 +3534,13 @@
         <v>6140</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -3731,13 +3551,13 @@
         <v>6150</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -3748,13 +3568,13 @@
         <v>7010</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -3765,13 +3585,13 @@
         <v>7020</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
@@ -3782,13 +3602,13 @@
         <v>7110</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -3799,13 +3619,13 @@
         <v>7120</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -3816,13 +3636,13 @@
         <v>7130</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -3833,13 +3653,13 @@
         <v>8010</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -3850,13 +3670,13 @@
         <v>8020</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -3867,13 +3687,13 @@
         <v>8110</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -3884,13 +3704,13 @@
         <v>8120</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -3901,13 +3721,13 @@
         <v>8130</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
@@ -3918,13 +3738,13 @@
         <v>9110</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="G59" t="s">
         <v>12</v>
@@ -3935,13 +3755,13 @@
         <v>9120</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -3952,13 +3772,13 @@
         <v>9130</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="G61" t="s">
         <v>12</v>
@@ -3990,10 +3810,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4001,10 +3821,10 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4012,10 +3832,10 @@
         <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4023,10 +3843,10 @@
         <v>1020</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4034,10 +3854,10 @@
         <v>1030</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4045,10 +3865,10 @@
         <v>1031</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4056,10 +3876,10 @@
         <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4067,10 +3887,10 @@
         <v>1041</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4078,10 +3898,10 @@
         <v>1050</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4089,10 +3909,10 @@
         <v>1060</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4100,10 +3920,10 @@
         <v>1070</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4111,10 +3931,10 @@
         <v>1080</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4122,10 +3942,10 @@
         <v>2010</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4133,10 +3953,10 @@
         <v>2020</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4144,10 +3964,10 @@
         <v>3010</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4155,10 +3975,10 @@
         <v>3020</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4166,10 +3986,10 @@
         <v>7020</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4177,10 +3997,10 @@
         <v>7040</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4188,10 +4008,10 @@
         <v>7050</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4199,10 +4019,10 @@
         <v>7060</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4210,10 +4030,10 @@
         <v>7070</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4221,10 +4041,10 @@
         <v>7080</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4232,10 +4052,10 @@
         <v>8010</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4243,10 +4063,10 @@
         <v>8020</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4254,10 +4074,10 @@
         <v>8030</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4265,10 +4085,10 @@
         <v>8040</v>
       </c>
       <c r="B27" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Achievements.xlsx
+++ b/Assets/Data/Achievements.xlsx
@@ -57,13 +57,13 @@
     <t>""</t>
   </si>
   <si>
-    <t>Recruit comrades using the recruitment command</t>
+    <t>Recruit comrades using the Recruit command</t>
   </si>
   <si>
     <t>編成コマンドで仲間を編成する</t>
   </si>
   <si>
-    <t>Arrange comrades using the formation command</t>
+    <t>Arrange comrades using the Formation command</t>
   </si>
   <si>
     <t>アイテムを使用していずれかのキャラのLvを上げる</t>
@@ -75,13 +75,13 @@
     <t>献上コマンドで装備を入手する</t>
   </si>
   <si>
-    <t>Acquire equipment through the offering command</t>
+    <t>Acquire equipment through the Offering command</t>
   </si>
   <si>
     <t>取引コマンドでアイテムか装備を入手する</t>
   </si>
   <si>
-    <t>Obtain items or equipment via the trade command</t>
+    <t>Obtain items or equipment via the Trade command</t>
   </si>
   <si>
     <t>仲間の装備を変更する</t>
@@ -389,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -403,16 +403,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,34 +464,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -463,7 +495,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,48 +531,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -527,21 +542,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,7 +556,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,31 +616,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,19 +646,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,19 +670,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,43 +724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,43 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -751,6 +751,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -761,6 +776,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -780,21 +804,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -806,8 +815,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -836,17 +847,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -855,145 +855,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
